--- a/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Gobierno integrado del portfolio de I+D con estrategia, presupuesto, riesgos, capacidad de ejecución, beneficios esperados y reasignación periódica de recursos.</t>
   </si>
   <si>
-    <t>Portfolio de innovación dinámico y AI-enabled, con priorización basada en escenarios, señales de mercado, probabilidad de éxito, ROI esperado y recomendaciones de asignación de capital.</t>
-  </si>
-  <si>
-    <t>AI-orchestrated product design; Smarter clinical trials; End-to-end autonomous drug discovery and development</t>
+    <t>Portfolio de innovación dinámico y basado en IA, con priorización basada en escenarios, señales de mercado, probabilidad de éxito, ROI esperado y recomendaciones de asignación de capital.</t>
+  </si>
+  <si>
+    <t>Diseño de producto orquestado por IA; Ensayos clínicos más inteligentes; Descubrimiento y desarrollo de fármacos autónomo de extremo a extremo</t>
   </si>
   <si>
     <t>¿Existe portfolio formal de iniciativas de I+D?
@@ -203,7 +203,7 @@
     <t>Motor inteligente de identificación y optimización de incentivos, con screening normativo, elegibilidad predictiva, generación asistida de documentación y alertas de cumplimiento.</t>
   </si>
   <si>
-    <t>Automated regulatory compliance; Financial rules and regulations interpretations; AI-orchestrated product design</t>
+    <t>Cumplimiento regulatorio automatizado; Interpretación de normas y regulación financiera; Diseño de producto orquestado por IA</t>
   </si>
   <si>
     <t>¿Se monitorizan fuentes de financiación e incentivos?
@@ -239,7 +239,7 @@
     <t>Medición avanzada de valor con modelos predictivos, análisis de contribución, escenarios de monetización y recomendaciones de inversión/desinversión en innovación.</t>
   </si>
   <si>
-    <t>End-to-end autonomous drug discovery and development; AI-orchestrated product design; Project-level recommendations</t>
+    <t>Descubrimiento y desarrollo de fármacos autónomo de extremo a extremo; Diseño de producto orquestado por IA; Recomendaciones a nivel de proyecto</t>
   </si>
   <si>
     <t>¿Se mide ROI de iniciativas de I+D?
@@ -275,10 +275,10 @@
     <t>Gobierno integrado con CRM, pricing, crédito, contratos, rentabilidad y forecast comercial, con workflow y reporting de cumplimiento.</t>
   </si>
   <si>
-    <t>Asistente AI para propuestas comerciales que recomienda condiciones, identifica riesgos, estima rentabilidad y guía aprobaciones según margen, cliente y probabilidad de conversión.</t>
-  </si>
-  <si>
-    <t>AI-powered RFP and knowledge assistant; Intelligent commercial operations; AI assistant for vehicle buying and leasing</t>
+    <t>Asistente IA para propuestas comerciales que recomienda condiciones, identifica riesgos, estima rentabilidad y guía aprobaciones según margen, cliente y probabilidad de conversión.</t>
+  </si>
+  <si>
+    <t>Asistente de RFP y de conocimiento impulsado por IA; Operaciones comerciales inteligentes; Asistente de IA para la compra y el leasing de vehículos</t>
   </si>
   <si>
     <t>¿Existen políticas financieras para ofertas y descuentos?
@@ -311,10 +311,10 @@
     <t>Evaluación integrada con pipeline, pricing, capacidad operativa, riesgos contractuales, forecast y priorización comercial.</t>
   </si>
   <si>
-    <t>AI/RFP assistant que resume requerimientos, estima economics, identifica riesgos, propone respuestas y prioriza oportunidades según valor ajustado por probabilidad y riesgo.</t>
-  </si>
-  <si>
-    <t>AI-powered RFP and knowledge assistant; Intelligent commercial operations; Hyper-personalized sales and marketing assistant</t>
+    <t>IA/RFP assistant que resume requerimientos, estima economics, identifica riesgos, propone respuestas y prioriza oportunidades según valor ajustado por probabilidad y riesgo.</t>
+  </si>
+  <si>
+    <t>Asistente de RFP y de conocimiento impulsado por IA; Operaciones comerciales inteligentes; Asistente hiperpersonalizado de ventas y marketing</t>
   </si>
   <si>
     <t>¿Se evalúan oportunidades con criterios homogéneos?
@@ -350,7 +350,7 @@
     <t>Scoring predictivo de riesgo comercial y exposición, con recomendaciones de condiciones, garantías, límites, pricing y acciones preventivas por cliente u oportunidad.</t>
   </si>
   <si>
-    <t>AI agents for credit underwriting; Recommend optimal payment terms to improve DSO; Intelligent commercial operations</t>
+    <t>Agentes de IA para el análisis de riesgo crediticio; Recomendación de condiciones de pago óptimas para mejorar el DSO; Operaciones comerciales inteligentes</t>
   </si>
   <si>
     <t>¿Se evalúa riesgo financiero de clientes y ofertas?
@@ -383,10 +383,10 @@
     <t>Reporting integrado de ventas, margen, cash, descuentos, forecast y acciones, con owners y revisión periódica de performance.</t>
   </si>
   <si>
-    <t>AI genera insights de performance comercial, identifica oportunidades de mejora, riesgos de margen, leakage y acciones personalizadas por cliente, canal o producto.</t>
-  </si>
-  <si>
-    <t>Intelligent commercial operations; Hyper-personalized sales and marketing assistant; Identify &amp; proactively correct revenue leakage</t>
+    <t>IA genera insights de performance comercial, identifica oportunidades de mejora, riesgos de margen, leakage y acciones personalizadas por cliente, canal o producto.</t>
+  </si>
+  <si>
+    <t>Operaciones comerciales inteligentes; Asistente hiperpersonalizado de ventas y marketing; Identificación y corrección proactiva de fugas de ingresos</t>
   </si>
   <si>
     <t>¿Se mide margen real vs ofertado?
@@ -422,10 +422,10 @@
     <t>Planificación integrada con S&amp;OP/IBP, presupuesto, forecast, capacidad, cash, riesgos y escenarios operativos.</t>
   </si>
   <si>
-    <t>Integrated business planning AI-enabled, con simulación de demanda, capacidad, costes, inventario, restricciones y recomendaciones de decisiones operativas-financieras.</t>
-  </si>
-  <si>
-    <t>Autonomous supply chain operations; Integrated business planning; Dynamic inventory management</t>
+    <t>Integrated business planning basado en IA, con simulación de demanda, capacidad, costes, inventario, restricciones y recomendaciones de decisiones operativas-financieras.</t>
+  </si>
+  <si>
+    <t>Operaciones autónomas de cadena de suministro; Planificación integrada de negocio; Gestión dinámica de inventario</t>
   </si>
   <si>
     <t>¿Se conecta la planificación financiera con demanda y capacidad?
@@ -458,10 +458,10 @@
     <t>Control integrado de costes con productividad, calidad, mantenimiento, logística, inventarios, acciones correctivas y forecast.</t>
   </si>
   <si>
-    <t>AI identifica patrones de coste, anomalías operativas, mantenimiento predictivo y oportunidades de eficiencia con recomendaciones cuantificadas.</t>
-  </si>
-  <si>
-    <t>AI-driven predictive maintenance; Autonomous field operations management; Recommend demand planning, product costing, and pricing setting</t>
+    <t>IA identifica patrones de coste, anomalías operativas, mantenimiento predictivo y oportunidades de eficiencia con recomendaciones cuantificadas.</t>
+  </si>
+  <si>
+    <t>Mantenimiento predictivo basado en IA; Gestión autónoma de operaciones de campo; Recomendación de planificación de demanda, coste de producto y fijación de precios</t>
   </si>
   <si>
     <t>¿Se conocen drivers de coste operativo?
@@ -494,10 +494,10 @@
     <t>Gestión integrada de inventario, demanda, producción, compras, servicio, cash y riesgo de obsolescencia, con acciones y seguimiento.</t>
   </si>
   <si>
-    <t>Optimización predictiva de inventario y working capital con AI, anticipando demanda, obsolescencia, rupturas, exceso de stock y necesidades de caja.</t>
-  </si>
-  <si>
-    <t>Dynamic inventory management; Autonomous supply chain operations; Predictive cash flow forecasting tool</t>
+    <t>Optimización predictiva de inventario y working capital con IA, anticipando demanda, obsolescencia, rupturas, exceso de stock y necesidades de caja.</t>
+  </si>
+  <si>
+    <t>Gestión dinámica de inventario; Operaciones autónomas de cadena de suministro; Herramienta predictiva de previsión de flujo de caja</t>
   </si>
   <si>
     <t>¿Se mide rotación, obsolescencia y cobertura?
@@ -530,10 +530,10 @@
     <t>Gestión integrada de resiliencia con coste, servicio, inventario, proveedores, logística, continuidad y planes de contingencia cuantificados.</t>
   </si>
   <si>
-    <t>AI monitoriza señales internas/externas de riesgo, simula impactos financieros y recomienda acciones de mitigación, sourcing, inventario o red logística.</t>
-  </si>
-  <si>
-    <t>Resilient logistics and planning; Autonomous supply chain operations; Autonomous drone-based infrastructure inspection</t>
+    <t>IA monitoriza señales internas/externas de riesgo, simula impactos financieros y recomienda acciones de mitigación, sourcing, inventario o red logística.</t>
+  </si>
+  <si>
+    <t>Logística y planificación resilientes; Operaciones autónomas de cadena de suministro; Inspección autónoma de infraestructuras con drones</t>
   </si>
   <si>
     <t>¿Se cuantifican riesgos de supply chain?
@@ -569,10 +569,10 @@
     <t>Pricing integrado con estrategia comercial, costes, competencia, elasticidad, margen, promociones y performance, con rutinas de revisión.</t>
   </si>
   <si>
-    <t>Pricing dinámico AI-enabled que recomienda precios y condiciones según demanda, elasticidad, inventario, cliente, competencia, costes y objetivos de margen.</t>
-  </si>
-  <si>
-    <t>Dynamic pricing and inventory optimization; Examine market trends, supplier behavior, and other factors to determine optimal prices; Recommend demand planning, product costing, and pricing setting</t>
+    <t>Pricing dinámico basado en IA que recomienda precios y condiciones según demanda, elasticidad, inventario, cliente, competencia, costes y objetivos de margen.</t>
+  </si>
+  <si>
+    <t>Precios dinámicos y optimización de inventario; Examen de tendencias de mercado, comportamiento de proveedores y otros factores para determinar precios óptimos; Recomendación de planificación de demanda, coste de producto y fijación de precios</t>
   </si>
   <si>
     <t>¿Existe estrategia de pricing documentada?
@@ -605,10 +605,10 @@
     <t>Rentabilidad integrada con pricing, mix, descuentos, promociones, servicio, canal, forecast y acciones comerciales.</t>
   </si>
   <si>
-    <t>Modelos AI identifican patrones de rentabilidad, leakage, cross-sell/upsell y recomendaciones de mix, cliente, canal y nivel de servicio.</t>
-  </si>
-  <si>
-    <t>Identify &amp; proactively correct revenue leakage; AI agents for customer success; Hyper-personalized sales and marketing assistant</t>
+    <t>Modelos IA identifican patrones de rentabilidad, leakage, cross-sell/upsell y recomendaciones de mix, cliente, canal y nivel de servicio.</t>
+  </si>
+  <si>
+    <t>Identificación y corrección proactiva de fugas de ingresos; Agentes de IA para el éxito del cliente; Asistente hiperpersonalizado de ventas y marketing</t>
   </si>
   <si>
     <t>¿Se mide rentabilidad por cliente/producto/canal?
@@ -641,10 +641,10 @@
     <t>Optimización integrada de promociones con demanda, pricing, inventario, margen, canal y aprendizaje post-campaña.</t>
   </si>
   <si>
-    <t>AI recomienda promociones, descuentos y condiciones óptimas, simulando elasticidad, canibalización, inventario, margen incremental y probabilidad de conversión.</t>
-  </si>
-  <si>
-    <t>Planning for promotions; Dynamic pricing and inventory optimization; Recommend demand planning, product costing, and pricing setting</t>
+    <t>IA recomienda promociones, descuentos y condiciones óptimas, simulando elasticidad, canibalización, inventario, margen incremental y probabilidad de conversión.</t>
+  </si>
+  <si>
+    <t>Planificación de promociones; Precios dinámicos y optimización de inventario; Recomendación de planificación de demanda, coste de producto y fijación de precios</t>
   </si>
   <si>
     <t>¿Se calcula ROI de promociones?
@@ -677,10 +677,10 @@
     <t>Margin management integrado con pricing, ventas, costes, mix, contratos, forecast y rutinas de gestión orientadas a acción.</t>
   </si>
   <si>
-    <t>AI detecta leakage y desviaciones tempranas, explica drivers de margen, recomienda acciones de precio/mix/coste y cuantifica impacto esperado en valor.</t>
-  </si>
-  <si>
-    <t>Identify &amp; proactively correct revenue leakage; FinanceAI Insights Platform; Generate account variance analysis and intelligent explanations</t>
+    <t>IA detecta leakage y desviaciones tempranas, explica drivers de margen, recomienda acciones de precio/mix/coste y cuantifica impacto esperado en valor.</t>
+  </si>
+  <si>
+    <t>Identificación y corrección proactiva de fugas de ingresos; FinanceAI Insights Platform; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Se monitoriza margen por driver?

--- a/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="273">
   <si>
     <t>Capacidad</t>
   </si>
@@ -870,6 +870,51 @@
   </si>
   <si>
     <t>5 - Avanzado/Referente: modelo maduro, estratégico, anticipativo y orientado a generación de valor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diseño de producto orquestado por IA; Ensayos clínicos más inteligentes; Descubrimiento autónomo de fármacos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumplimiento regulatorio automatizado; Interpretación de normativa financiera; Diseño de producto orquestado por IA; Determinación de elegibilidad para incentivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descubrimiento autónomo de fármacos; Diseño de producto orquestado por IA; Recomendaciones de acción a nivel de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de RFP y de conocimiento comercial; Operaciones comerciales inteligentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de RFP y de conocimiento comercial; Operaciones comerciales inteligentes; Personalización de ventas y marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentes de IA para análisis de riesgo crediticio; Condiciones de pago óptimas para el DSO; Operaciones comerciales inteligentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operaciones comerciales inteligentes; Personalización de ventas y marketing; Detección de fugas de ingresos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantenimiento predictivo de activos; Recomendación de demanda, coste y precio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestión dinámica de inventario; Operaciones autónomas de cadena de suministro; Previsión predictiva de flujo de caja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación logística resiliente; Operaciones autónomas de cadena de suministro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio dinámico y optimización de inventario; Precio óptimo a partir de señales de mercado; Recomendación de demanda, coste y precio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de fugas de ingresos; Agentes de IA para el éxito del cliente; Personalización de ventas y marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación de promociones; Precio dinámico y optimización de inventario; Recomendación de demanda, coste y precio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de fugas de ingresos; Analista digital de Finanzas bajo demanda; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantenimiento predictivo de activos; Gestión autónoma de operaciones de campo; Recomendación de demanda, coste y precio</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1665,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1678,7 +1723,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1736,7 +1781,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1794,7 +1839,7 @@
         <v>59</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1852,7 +1897,7 @@
         <v>71</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1910,7 +1955,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1968,7 +2013,7 @@
         <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>94</v>
+        <v>263</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2026,7 +2071,7 @@
         <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2142,7 +2187,7 @@
         <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2200,7 +2245,7 @@
         <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2258,7 +2303,7 @@
         <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2316,7 +2361,7 @@
         <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2374,7 +2419,7 @@
         <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2432,7 +2477,7 @@
         <v>183</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2490,7 +2535,7 @@
         <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3391,7 +3436,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G17" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -3422,7 +3467,7 @@
         <v>41</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3453,7 +3498,7 @@
         <v>52</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3484,7 +3529,7 @@
         <v>63</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3515,7 +3560,7 @@
         <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3546,7 +3591,7 @@
         <v>86</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3577,7 +3622,7 @@
         <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>263</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3608,7 +3653,7 @@
         <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3670,7 +3715,7 @@
         <v>131</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3701,7 +3746,7 @@
         <v>142</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3732,7 +3777,7 @@
         <v>153</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3763,7 +3808,7 @@
         <v>165</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3794,7 +3839,7 @@
         <v>176</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3825,7 +3870,7 @@
         <v>187</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3856,7 +3901,7 @@
         <v>198</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3916,7 +3961,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3933,7 +3978,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -3950,7 +3995,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>48</v>
@@ -3967,7 +4012,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>59</v>
@@ -3984,7 +4029,7 @@
         <v>65</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>71</v>
@@ -4001,7 +4046,7 @@
         <v>76</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>82</v>
@@ -4018,7 +4063,7 @@
         <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>93</v>
@@ -4035,7 +4080,7 @@
         <v>98</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>104</v>
@@ -4069,7 +4114,7 @@
         <v>121</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>127</v>
@@ -4086,7 +4131,7 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>138</v>
@@ -4103,7 +4148,7 @@
         <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>149</v>
@@ -4120,7 +4165,7 @@
         <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>161</v>
@@ -4137,7 +4182,7 @@
         <v>166</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>172</v>
@@ -4154,7 +4199,7 @@
         <v>177</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>183</v>
@@ -4171,7 +4216,7 @@
         <v>188</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>194</v>

--- a/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
@@ -131,7 +131,7 @@
     <t>Gobierno integrado del portfolio de I+D con estrategia, presupuesto, riesgos, capacidad de ejecución, beneficios esperados y reasignación periódica de recursos.</t>
   </si>
   <si>
-    <t>Portfolio de innovación dinámico y basado en IA, con priorización basada en escenarios, señales de mercado, probabilidad de éxito, ROI esperado y recomendaciones de asignación de capital.</t>
+    <t>Cartera de innovación dinámica y basada en IA, con priorización por escenarios, señales de mercado, probabilidad de éxito y ROI esperado, y recomendación de asignación de capital.</t>
   </si>
   <si>
     <t>Diseño de producto orquestado por IA; Ensayos clínicos más inteligentes; Descubrimiento y desarrollo de fármacos autónomo de extremo a extremo</t>
@@ -200,7 +200,7 @@
     <t>Gestión integrada de funding con portfolio, presupuesto, contabilidad, fiscalidad, reporting y evidencias requeridas por organismos financiadores.</t>
   </si>
   <si>
-    <t>Motor inteligente de identificación y optimización de incentivos, con screening normativo, elegibilidad predictiva, generación asistida de documentación y alertas de cumplimiento.</t>
+    <t>Motor inteligente de identificación y optimización de incentivos, con cribado normativo, elegibilidad predictiva, generación asistida de documentación y alertas de cumplimiento.</t>
   </si>
   <si>
     <t>Cumplimiento regulatorio automatizado; Interpretación de normas y regulación financiera; Diseño de producto orquestado por IA</t>
@@ -311,7 +311,7 @@
     <t>Evaluación integrada con pipeline, pricing, capacidad operativa, riesgos contractuales, forecast y priorización comercial.</t>
   </si>
   <si>
-    <t>IA/RFP assistant que resume requerimientos, estima economics, identifica riesgos, propone respuestas y prioriza oportunidades según valor ajustado por probabilidad y riesgo.</t>
+    <t>Asistente de IA para RFP que resume los requisitos, estima la rentabilidad esperada, identifica riesgos, propone respuestas y prioriza oportunidades por valor ajustado a probabilidad y riesgo.</t>
   </si>
   <si>
     <t>Asistente de RFP y de conocimiento impulsado por IA; Operaciones comerciales inteligentes; Asistente hiperpersonalizado de ventas y marketing</t>
@@ -347,7 +347,7 @@
     <t>Riesgo comercial integrado con CRM, contratos, O2C, pricing, margen, cash y límites de exposición, con alertas y seguimiento.</t>
   </si>
   <si>
-    <t>Scoring predictivo de riesgo comercial y exposición, con recomendaciones de condiciones, garantías, límites, pricing y acciones preventivas por cliente u oportunidad.</t>
+    <t>Puntuación predictiva del riesgo comercial y de la exposición, con recomendación de condiciones, garantías, límites, precio y acciones preventivas por cliente u oportunidad.</t>
   </si>
   <si>
     <t>Agentes de IA para el análisis de riesgo crediticio; Recomendación de condiciones de pago óptimas para mejorar el DSO; Operaciones comerciales inteligentes</t>
@@ -383,7 +383,7 @@
     <t>Reporting integrado de ventas, margen, cash, descuentos, forecast y acciones, con owners y revisión periódica de performance.</t>
   </si>
   <si>
-    <t>IA genera insights de performance comercial, identifica oportunidades de mejora, riesgos de margen, leakage y acciones personalizadas por cliente, canal o producto.</t>
+    <t>IA genera conclusiones de rendimiento comercial, identifica oportunidades de mejora, riesgos de margen, fuga de ingresos y acciones personalizadas por cliente, canal o producto.</t>
   </si>
   <si>
     <t>Operaciones comerciales inteligentes; Asistente hiperpersonalizado de ventas y marketing; Identificación y corrección proactiva de fugas de ingresos</t>
@@ -422,7 +422,7 @@
     <t>Planificación integrada con S&amp;OP/IBP, presupuesto, forecast, capacidad, cash, riesgos y escenarios operativos.</t>
   </si>
   <si>
-    <t>Integrated business planning basado en IA, con simulación de demanda, capacidad, costes, inventario, restricciones y recomendaciones de decisiones operativas-financieras.</t>
+    <t>Planificación integrada de negocio basada en IA, con simulación de demanda, capacidad, costes, inventario y restricciones, y recomendación de decisiones operativas y financieras.</t>
   </si>
   <si>
     <t>Operaciones autónomas de cadena de suministro; Planificación integrada de negocio; Gestión dinámica de inventario</t>
@@ -494,7 +494,7 @@
     <t>Gestión integrada de inventario, demanda, producción, compras, servicio, cash y riesgo de obsolescencia, con acciones y seguimiento.</t>
   </si>
   <si>
-    <t>Optimización predictiva de inventario y working capital con IA, anticipando demanda, obsolescencia, rupturas, exceso de stock y necesidades de caja.</t>
+    <t>Optimización predictiva de inventario y capital circulante con IA, anticipando demanda, obsolescencia, rupturas, exceso de stock y necesidades de caja.</t>
   </si>
   <si>
     <t>Gestión dinámica de inventario; Operaciones autónomas de cadena de suministro; Herramienta predictiva de previsión de flujo de caja</t>
@@ -530,7 +530,7 @@
     <t>Gestión integrada de resiliencia con coste, servicio, inventario, proveedores, logística, continuidad y planes de contingencia cuantificados.</t>
   </si>
   <si>
-    <t>IA monitoriza señales internas/externas de riesgo, simula impactos financieros y recomienda acciones de mitigación, sourcing, inventario o red logística.</t>
+    <t>IA monitoriza señales internas/externas de riesgo, simula impactos financieros y recomienda acciones de mitigación, aprovisionamiento, inventario o red logística.</t>
   </si>
   <si>
     <t>Logística y planificación resilientes; Operaciones autónomas de cadena de suministro; Inspección autónoma de infraestructuras con drones</t>
@@ -569,7 +569,7 @@
     <t>Pricing integrado con estrategia comercial, costes, competencia, elasticidad, margen, promociones y performance, con rutinas de revisión.</t>
   </si>
   <si>
-    <t>Pricing dinámico basado en IA que recomienda precios y condiciones según demanda, elasticidad, inventario, cliente, competencia, costes y objetivos de margen.</t>
+    <t>Fijación dinámica de precios basada en IA, que recomienda precio y condiciones según demanda, elasticidad, inventario, cliente, competencia, costes y objetivos de margen.</t>
   </si>
   <si>
     <t>Precios dinámicos y optimización de inventario; Examen de tendencias de mercado, comportamiento de proveedores y otros factores para determinar precios óptimos; Recomendación de planificación de demanda, coste de producto y fijación de precios</t>
@@ -605,7 +605,7 @@
     <t>Rentabilidad integrada con pricing, mix, descuentos, promociones, servicio, canal, forecast y acciones comerciales.</t>
   </si>
   <si>
-    <t>Modelos IA identifican patrones de rentabilidad, leakage, cross-sell/upsell y recomendaciones de mix, cliente, canal y nivel de servicio.</t>
+    <t>Modelos IA identifican patrones de rentabilidad, fuga de ingresos, venta cruzada y ampliación y recomendaciones de mix, cliente, canal y nivel de servicio.</t>
   </si>
   <si>
     <t>Identificación y corrección proactiva de fugas de ingresos; Agentes de IA para el éxito del cliente; Asistente hiperpersonalizado de ventas y marketing</t>
@@ -677,7 +677,7 @@
     <t>Margin management integrado con pricing, ventas, costes, mix, contratos, forecast y rutinas de gestión orientadas a acción.</t>
   </si>
   <si>
-    <t>IA detecta leakage y desviaciones tempranas, explica drivers de margen, recomienda acciones de precio/mix/coste y cuantifica impacto esperado en valor.</t>
+    <t>IA detecta fuga de ingresos y desviaciones tempranas, explica drivers de margen, recomienda acciones de precio/mix/coste y cuantifica impacto esperado en valor.</t>
   </si>
   <si>
     <t>Identificación y corrección proactiva de fugas de ingresos; FinanceAI Insights Platform; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>

--- a/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Negocio_BU_assessment_ready_AI_v0.xlsx
@@ -146,7 +146,7 @@
     <t>Portfolio de I+D; criterios de priorización; actas de comité; business cases; presupuesto por iniciativa; matriz de ownership.</t>
   </si>
   <si>
-    <t>Diseñar modelo de gobierno del portfolio de I+D con criterios de valor, riesgo, alineamiento estratégico, funding y seguimiento periódico.</t>
+    <t>Diseñar modelo de gobierno de la cartera de I+D con criterios de valor, riesgo, alineamiento estratégico, financiación y seguimiento periódico.</t>
   </si>
   <si>
     <t>1.2 Planificación y control económico de proyectos de I+D</t>
@@ -179,7 +179,7 @@
     <t>Presupuesto de I+D; forecast por proyecto; informes de desviaciones; hitos técnicos; costes reales; actas de seguimiento.</t>
   </si>
   <si>
-    <t>Implantar modelo de control económico de proyectos de I+D con presupuesto, forecast, hitos, desviaciones, riesgos y acciones correctivas.</t>
+    <t>Implantar modelo de control económico de proyectos de I+D con presupuesto, previsión, hitos, desviaciones, riesgos y acciones correctivas.</t>
   </si>
   <si>
     <t>1.3 Financiación, subvenciones e incentivos de I+D</t>
@@ -215,7 +215,7 @@
     <t>Mapa de incentivos; expedientes de subvención; justificaciones; documentación técnica; registros contables; calendario de obligaciones.</t>
   </si>
   <si>
-    <t>Crear proceso estructurado de funding e incentivos de I+D con screening de elegibilidad, evidencias, workflow de aprobación y tracking financiero.</t>
+    <t>Crear proceso estructurado de financiación e incentivos de I+D con análisis de elegibilidad, evidencias, flujo de aprobación y seguimiento financiero.</t>
   </si>
   <si>
     <t>1.4 Medición de valor y retorno de la innovación</t>
@@ -251,7 +251,7 @@
     <t>KPIs de innovación; benefit tracking; business cases; informes post-implementación; decisiones de portfolio; lecciones aprendidas.</t>
   </si>
   <si>
-    <t>Definir modelo de medición de valor de I+D con KPIs, beneficios esperados/reales, owners, revisión de portfolio y aprendizaje recurrente.</t>
+    <t>Definir modelo de medición de valor de I+D con KPIs, beneficios esperados y reales, responsables, revisión de la cartera y aprendizaje recurrente.</t>
   </si>
   <si>
     <t>Financiación de ventas comerciales</t>
@@ -290,7 +290,7 @@
     <t>Políticas comerciales; matriz de descuentos; aprobaciones; CRM; ofertas; contratos; análisis de margen por oportunidad.</t>
   </si>
   <si>
-    <t>Diseñar gobierno financiero de propuestas comerciales con reglas de margen, descuentos, riesgos, aprobaciones y trazabilidad end-to-end.</t>
+    <t>Diseñar gobierno financiero de propuestas comerciales con reglas de margen, descuentos, riesgos, aprobaciones y trazabilidad de principio a fin.</t>
   </si>
   <si>
     <t>2.2 Evaluación financiera de oportunidades, RFPs y ofertas</t>
@@ -326,7 +326,7 @@
     <t>RFPs; plantillas de análisis; pipeline comercial; modelos de margen; actas de bid/no-bid; aprobaciones de ofertas.</t>
   </si>
   <si>
-    <t>Implantar modelo de evaluación financiera de oportunidades y RFPs con economics, riesgos, capacidad, probabilidad y priorización de pipeline.</t>
+    <t>Implantar modelo de evaluación financiera de oportunidades y RFPs con análisis económico, riesgos, capacidad, probabilidad y priorización de la cartera comercial.</t>
   </si>
   <si>
     <t>2.3 Gestión de riesgos comerciales y exposición financiera</t>
@@ -362,7 +362,7 @@
     <t>Política de crédito; límites; exposición por cliente; contratos; términos comerciales; aging; aprobaciones de riesgo.</t>
   </si>
   <si>
-    <t>Construir modelo de riesgo comercial financiero con scoring, límites, términos, exposición, alertas y workflow de aprobación.</t>
+    <t>Construir modelo de riesgo comercial financiero con puntuación de riesgo, límites, condiciones, exposición, alertas y flujo de aprobación.</t>
   </si>
   <si>
     <t>2.4 Seguimiento de performance comercial y rentabilidad de ventas</t>
@@ -398,7 +398,7 @@
     <t>Dashboard comercial-financiero; pipeline; márgenes; descuentos; revenue leakage; actas de performance; acciones comerciales.</t>
   </si>
   <si>
-    <t>Rediseñar reporting comercial-financiero con KPIs de margen, conversión, leakage, forecast, owners y acciones de mejora.</t>
+    <t>Rediseñar los informes comercial-financieros con KPIs de margen, conversión, fugas, previsión, responsables y acciones de mejora.</t>
   </si>
   <si>
     <t>Financiación de la fabricación y la cadena de suministro</t>
@@ -437,7 +437,7 @@
     <t>Plan operativo-financiero; S&amp;OP/IBP; forecast de demanda; capacidad; costes logísticos; inventarios; escenarios.</t>
   </si>
   <si>
-    <t>Implantar planificación financiera integrada de operaciones y supply chain con drivers, escenarios, capacidad, inventario y forecast.</t>
+    <t>Implantar planificación financiera integrada de operaciones y cadena de suministro con drivers, escenarios, capacidad, inventario y previsión.</t>
   </si>
   <si>
     <t>3.2 Control de costes de fabricación, logística y servicio</t>
@@ -509,7 +509,7 @@
     <t>KPIs de inventario; DIO; obsolescencia; stock-outs; slow movers; forecast de inventario; reporting de working capital.</t>
   </si>
   <si>
-    <t>Implantar modelo financiero de inventarios y working capital con KPIs, escenarios, alertas de obsolescencia y acciones de optimización.</t>
+    <t>Implantar modelo financiero de inventarios y capital circulante con KPIs, escenarios, alertas de obsolescencia y acciones de optimización.</t>
   </si>
   <si>
     <t>3.4 Resiliencia, riesgo y eficiencia de la cadena de suministro</t>
@@ -545,7 +545,7 @@
     <t>Mapa de riesgos; escenarios; proveedores críticos; planes de contingencia; KPIs de servicio; costes logísticos; análisis de impacto.</t>
   </si>
   <si>
-    <t>Desarrollar modelo financiero de resiliencia supply chain con riesgos, escenarios, impacto económico, planes de mitigación y seguimiento.</t>
+    <t>Desarrollar modelo financiero de resiliencia de la cadena de suministro con riesgos, escenarios, impacto económico, planes de mitigación y seguimiento.</t>
   </si>
   <si>
     <t>Precios y rentabilidad</t>
@@ -584,7 +584,7 @@
     <t>Política de pricing; catálogo de precios; matriz de descuentos; aprobaciones; análisis competitivo; reporting de margen.</t>
   </si>
   <si>
-    <t>Definir modelo de gobierno de pricing con estrategia, roles, reglas, descuentos, excepciones, KPIs y ciclo de revisión.</t>
+    <t>Definir modelo de gobierno de precios con estrategia, roles, reglas, descuentos, excepciones, KPIs y ciclo de revisión.</t>
   </si>
   <si>
     <t>4.2 Modelos de rentabilidad por cliente, producto y canal</t>
@@ -620,7 +620,7 @@
     <t>Modelo de rentabilidad; P&amp;L por dimensión; coste de servir; márgenes; descuentos; análisis de leakage; acciones comerciales.</t>
   </si>
   <si>
-    <t>Construir modelo granular de rentabilidad con coste de servir, margen neto, leakage, segmentación y acciones por cliente/producto/canal.</t>
+    <t>Construir modelo granular de rentabilidad con coste de servir, margen neto, fugas, segmentación y acciones por cliente, producto y canal.</t>
   </si>
   <si>
     <t>4.3 Optimización de promociones, descuentos y condiciones</t>
@@ -656,7 +656,7 @@
     <t>Calendario promocional; análisis ROI; baseline/uplift; descuentos; margen incremental; post-mortems; decisiones de pricing.</t>
   </si>
   <si>
-    <t>Implantar modelo de optimización promocional con ROI, uplift, margen, elasticidad, canibalización y recomendaciones de descuento.</t>
+    <t>Implantar modelo de optimización promocional con ROI, incremento de ventas, margen, elasticidad, canibalización y recomendaciones de descuento.</t>
   </si>
   <si>
     <t>4.4 Seguimiento de margen, leakage y creación de valor</t>
@@ -692,7 +692,7 @@
     <t>Dashboard de margen; análisis de leakage; variaciones de precio/mix/coste; contratos; acciones; seguimiento de beneficios.</t>
   </si>
   <si>
-    <t>Crear modelo de margin performance management con drivers, leakage, owners, acciones, forecast e impacto económico cuantificado.</t>
+    <t>Crear modelo de gestión del rendimiento del margen con drivers, fugas, responsables, acciones, previsión e impacto económico cuantificado.</t>
   </si>
   <si>
     <t>Score global dominio</t>
